--- a/sources/table_normalization/xlsx/economy-table17.xlsx
+++ b/sources/table_normalization/xlsx/economy-table17.xlsx
@@ -655,7 +655,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1034,7 +1034,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1162,11 +1162,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1192,28 +1192,125 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1224,81 +1321,86 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1316,30 +1418,6 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1358,86 +1436,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1985,27 +1991,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="145.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
       <c r="O1" s="27"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="88"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122"/>
     </row>
     <row r="2" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -2029,31 +2035,31 @@
       <c r="S2" s="36"/>
     </row>
     <row r="3" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="100" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="101"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="98" t="s">
+      <c r="M3" s="127"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
     </row>
     <row r="4" spans="1:256" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -2076,68 +2082,68 @@
       <c r="S4" s="14"/>
     </row>
     <row r="5" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="48" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="113"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="116" t="s">
+      <c r="G5" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="116"/>
+      <c r="H5" s="114"/>
       <c r="I5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="117" t="s">
+      <c r="L5" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="118" t="s">
+      <c r="M5" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="118" t="s">
+      <c r="N5" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="120" t="s">
+      <c r="P5" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="121" t="s">
+      <c r="Q5" s="115"/>
+      <c r="R5" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="121" t="s">
+      <c r="S5" s="53" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:256" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="50"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
+      <c r="A6" s="116"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="116"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="M6" s="28"/>
       <c r="N6" s="28"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
+      <c r="P6" s="116"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="116"/>
+      <c r="S6" s="116"/>
     </row>
     <row r="7" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
@@ -2145,7 +2151,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="15"/>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="74" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="16" t="s">
@@ -2166,7 +2172,7 @@
       <c r="N7" s="7">
         <v>206</v>
       </c>
-      <c r="P7" s="78" t="s">
+      <c r="P7" s="101" t="s">
         <v>17</v>
       </c>
       <c r="Q7" s="37" t="s">
@@ -2180,11 +2186,11 @@
       </c>
     </row>
     <row r="8" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="7">
         <v>2731.5810000000001</v>
       </c>
@@ -2192,7 +2198,7 @@
         <v>2557.4</v>
       </c>
       <c r="F8" s="15"/>
-      <c r="G8" s="74"/>
+      <c r="G8" s="75"/>
       <c r="H8" s="16" t="s">
         <v>20</v>
       </c>
@@ -2211,7 +2217,7 @@
       <c r="N8" s="7">
         <v>3063</v>
       </c>
-      <c r="P8" s="79"/>
+      <c r="P8" s="108"/>
       <c r="Q8" s="37" t="s">
         <v>23</v>
       </c>
@@ -2223,11 +2229,11 @@
       </c>
     </row>
     <row r="9" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="7">
         <v>2508.6979999999999</v>
       </c>
@@ -2235,7 +2241,7 @@
         <v>2305.6</v>
       </c>
       <c r="F9" s="15"/>
-      <c r="G9" s="74"/>
+      <c r="G9" s="75"/>
       <c r="H9" s="16" t="s">
         <v>25</v>
       </c>
@@ -2254,7 +2260,7 @@
       <c r="N9" s="9">
         <v>3.25</v>
       </c>
-      <c r="P9" s="80"/>
+      <c r="P9" s="109"/>
       <c r="Q9" s="37" t="s">
         <v>27</v>
       </c>
@@ -2266,13 +2272,13 @@
       </c>
     </row>
     <row r="10" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="105" t="s">
+      <c r="A10" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="7">
         <v>1746.5930000000001</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>1633.6</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="75"/>
+      <c r="G10" s="76"/>
       <c r="H10" s="16" t="s">
         <v>30</v>
       </c>
@@ -2299,10 +2305,10 @@
       <c r="N10" s="7">
         <v>212</v>
       </c>
-      <c r="P10" s="58" t="s">
+      <c r="P10" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="Q10" s="59"/>
+      <c r="Q10" s="107"/>
       <c r="R10" s="7">
         <v>38218</v>
       </c>
@@ -2311,11 +2317,11 @@
       </c>
     </row>
     <row r="11" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="106"/>
-      <c r="B11" s="56" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="57"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="7">
         <v>422.661</v>
       </c>
@@ -2323,7 +2329,7 @@
         <v>372.9</v>
       </c>
       <c r="F11" s="15"/>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="74" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="16" t="s">
@@ -2344,7 +2350,7 @@
       <c r="N11" s="7">
         <v>71</v>
       </c>
-      <c r="P11" s="78" t="s">
+      <c r="P11" s="101" t="s">
         <v>37</v>
       </c>
       <c r="Q11" s="38" t="s">
@@ -2358,11 +2364,11 @@
       </c>
     </row>
     <row r="12" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="106"/>
-      <c r="B12" s="56" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="7">
         <v>287.40499999999997</v>
       </c>
@@ -2370,7 +2376,7 @@
         <v>224.9</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="76"/>
+      <c r="G12" s="77"/>
       <c r="H12" s="16" t="s">
         <v>39</v>
       </c>
@@ -2380,16 +2386,16 @@
       <c r="J12" s="9">
         <v>11.39</v>
       </c>
-      <c r="L12" s="117" t="s">
+      <c r="L12" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="118" t="s">
+      <c r="M12" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="119" t="s">
+      <c r="N12" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="P12" s="81"/>
+      <c r="P12" s="102"/>
       <c r="Q12" s="38" t="s">
         <v>23</v>
       </c>
@@ -2401,11 +2407,11 @@
       </c>
     </row>
     <row r="13" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="106"/>
-      <c r="B13" s="56" t="s">
+      <c r="A13" s="72"/>
+      <c r="B13" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="89"/>
       <c r="D13" s="7">
         <v>-26.248999999999999</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>-13.4</v>
       </c>
       <c r="F13" s="15"/>
-      <c r="G13" s="77"/>
+      <c r="G13" s="78"/>
       <c r="H13" s="16" t="s">
         <v>42</v>
       </c>
@@ -2432,7 +2438,7 @@
       <c r="N13" s="7">
         <v>3533597</v>
       </c>
-      <c r="P13" s="82"/>
+      <c r="P13" s="103"/>
       <c r="Q13" s="37" t="s">
         <v>27</v>
       </c>
@@ -2444,11 +2450,11 @@
       </c>
     </row>
     <row r="14" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="56" t="s">
+      <c r="A14" s="73"/>
+      <c r="B14" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="57"/>
+      <c r="C14" s="89"/>
       <c r="D14" s="7">
         <v>78.287999999999997</v>
       </c>
@@ -2456,7 +2462,7 @@
         <v>87.5</v>
       </c>
       <c r="F14" s="15"/>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="74" t="s">
         <v>45</v>
       </c>
       <c r="H14" s="16" t="s">
@@ -2477,23 +2483,23 @@
       <c r="N14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="108" t="s">
+      <c r="P14" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="Q14" s="122"/>
-      <c r="R14" s="121" t="s">
+      <c r="Q14" s="100"/>
+      <c r="R14" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="121" t="s">
+      <c r="S14" s="53" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="7">
         <v>684.83500000000004</v>
       </c>
@@ -2501,7 +2507,7 @@
         <v>660.1</v>
       </c>
       <c r="F15" s="15"/>
-      <c r="G15" s="77"/>
+      <c r="G15" s="78"/>
       <c r="H15" s="16" t="s">
         <v>50</v>
       </c>
@@ -2520,7 +2526,7 @@
       <c r="N15" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="P15" s="124" t="s">
+      <c r="P15" s="62" t="s">
         <v>52</v>
       </c>
       <c r="Q15" s="37" t="s">
@@ -2771,11 +2777,11 @@
       <c r="IV15" s="40"/>
     </row>
     <row r="16" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="7">
         <v>390.21499999999997</v>
       </c>
@@ -2783,7 +2789,7 @@
         <v>428.9</v>
       </c>
       <c r="F16" s="15"/>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="74" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="17" t="s">
@@ -2805,7 +2811,7 @@
       <c r="N16" s="7">
         <v>250000</v>
       </c>
-      <c r="P16" s="125"/>
+      <c r="P16" s="63"/>
       <c r="Q16" s="37" t="s">
         <v>58</v>
       </c>
@@ -3054,11 +3060,11 @@
       <c r="IV16" s="40"/>
     </row>
     <row r="17" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="99"/>
       <c r="D17" s="7">
         <v>1843.8409999999999</v>
       </c>
@@ -3066,7 +3072,7 @@
         <v>1659.8</v>
       </c>
       <c r="F17" s="15"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="77"/>
       <c r="H17" s="17" t="s">
         <v>60</v>
       </c>
@@ -3085,7 +3091,7 @@
       <c r="N17" s="29">
         <v>90</v>
       </c>
-      <c r="P17" s="125"/>
+      <c r="P17" s="63"/>
       <c r="Q17" s="37" t="s">
         <v>62</v>
       </c>
@@ -3334,11 +3340,11 @@
       <c r="IV17" s="40"/>
     </row>
     <row r="18" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="53"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="7">
         <v>222.88300000000001</v>
       </c>
@@ -3346,7 +3352,7 @@
         <v>251.8</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="77"/>
       <c r="H18" s="17" t="s">
         <v>64</v>
       </c>
@@ -3365,7 +3371,7 @@
       <c r="N18" s="29">
         <v>98</v>
       </c>
-      <c r="P18" s="125"/>
+      <c r="P18" s="63"/>
       <c r="Q18" s="37" t="s">
         <v>66</v>
       </c>
@@ -3614,13 +3620,13 @@
       <c r="IV18" s="40"/>
     </row>
     <row r="19" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="57"/>
+      <c r="C19" s="89"/>
       <c r="D19" s="7">
         <v>66.988</v>
       </c>
@@ -3628,7 +3634,7 @@
         <v>87.3</v>
       </c>
       <c r="F19" s="15"/>
-      <c r="G19" s="76"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="17" t="s">
         <v>67</v>
       </c>
@@ -3647,7 +3653,7 @@
       <c r="N19" s="29">
         <v>92</v>
       </c>
-      <c r="P19" s="125"/>
+      <c r="P19" s="63"/>
       <c r="Q19" s="37" t="s">
         <v>69</v>
       </c>
@@ -3896,11 +3902,11 @@
       <c r="IV19" s="40"/>
     </row>
     <row r="20" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106"/>
-      <c r="B20" s="56" t="s">
+      <c r="A20" s="72"/>
+      <c r="B20" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="57"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="7">
         <v>45.606999999999999</v>
       </c>
@@ -3908,7 +3914,7 @@
         <v>75.8</v>
       </c>
       <c r="F20" s="15"/>
-      <c r="G20" s="77"/>
+      <c r="G20" s="78"/>
       <c r="H20" s="17" t="s">
         <v>70</v>
       </c>
@@ -3927,7 +3933,7 @@
       <c r="N20" s="29">
         <v>64</v>
       </c>
-      <c r="P20" s="126"/>
+      <c r="P20" s="64"/>
       <c r="Q20" s="37" t="s">
         <v>72</v>
       </c>
@@ -4176,11 +4182,11 @@
       <c r="IV20" s="40"/>
     </row>
     <row r="21" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="106"/>
-      <c r="B21" s="56" t="s">
+      <c r="A21" s="72"/>
+      <c r="B21" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="57"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="7">
         <v>58.280999999999999</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>63.6</v>
       </c>
       <c r="F21" s="15"/>
-      <c r="G21" s="73" t="s">
+      <c r="G21" s="74" t="s">
         <v>73</v>
       </c>
       <c r="H21" s="16" t="s">
@@ -4209,7 +4215,7 @@
       <c r="N21" s="29">
         <v>99</v>
       </c>
-      <c r="P21" s="124" t="s">
+      <c r="P21" s="62" t="s">
         <v>76</v>
       </c>
       <c r="Q21" s="37" t="s">
@@ -4460,11 +4466,11 @@
       <c r="IV21" s="40"/>
     </row>
     <row r="22" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="106"/>
-      <c r="B22" s="56" t="s">
+      <c r="A22" s="72"/>
+      <c r="B22" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="57"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="7">
         <v>23.728000000000002</v>
       </c>
@@ -4472,7 +4478,7 @@
         <v>21.2</v>
       </c>
       <c r="F22" s="15"/>
-      <c r="G22" s="76"/>
+      <c r="G22" s="77"/>
       <c r="H22" s="16" t="s">
         <v>78</v>
       </c>
@@ -4491,7 +4497,7 @@
       <c r="N22" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="P22" s="126"/>
+      <c r="P22" s="64"/>
       <c r="Q22" s="37" t="s">
         <v>80</v>
       </c>
@@ -4740,11 +4746,11 @@
       <c r="IV22" s="40"/>
     </row>
     <row r="23" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
-      <c r="B23" s="56" t="s">
+      <c r="A23" s="73"/>
+      <c r="B23" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="7">
         <v>28.279</v>
       </c>
@@ -4752,7 +4758,7 @@
         <v>3.6</v>
       </c>
       <c r="F23" s="15"/>
-      <c r="G23" s="76"/>
+      <c r="G23" s="77"/>
       <c r="H23" s="16" t="s">
         <v>81</v>
       </c>
@@ -4771,7 +4777,7 @@
       <c r="N23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="P23" s="124" t="s">
+      <c r="P23" s="62" t="s">
         <v>83</v>
       </c>
       <c r="Q23" s="37" t="s">
@@ -5022,11 +5028,11 @@
       <c r="IV23" s="40"/>
     </row>
     <row r="24" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="62"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="7">
         <v>374.23</v>
       </c>
@@ -5034,7 +5040,7 @@
         <v>61.3</v>
       </c>
       <c r="F24" s="15"/>
-      <c r="G24" s="77"/>
+      <c r="G24" s="78"/>
       <c r="H24" s="16" t="s">
         <v>86</v>
       </c>
@@ -5044,16 +5050,16 @@
       <c r="J24" s="9">
         <v>5.76</v>
       </c>
-      <c r="L24" s="117" t="s">
+      <c r="L24" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="M24" s="118" t="s">
+      <c r="M24" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="N24" s="118" t="s">
+      <c r="N24" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="P24" s="125"/>
+      <c r="P24" s="63"/>
       <c r="Q24" s="37" t="s">
         <v>88</v>
       </c>
@@ -5302,13 +5308,13 @@
       <c r="IV24" s="40"/>
     </row>
     <row r="25" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="57"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="7">
         <v>384.52600000000001</v>
       </c>
@@ -5316,7 +5322,7 @@
         <v>34.799999999999997</v>
       </c>
       <c r="F25" s="15"/>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="74" t="s">
         <v>89</v>
       </c>
       <c r="H25" s="16" t="s">
@@ -5337,7 +5343,7 @@
       <c r="N25" s="31">
         <v>4148</v>
       </c>
-      <c r="P25" s="126"/>
+      <c r="P25" s="64"/>
       <c r="Q25" s="37" t="s">
         <v>92</v>
       </c>
@@ -5586,11 +5592,11 @@
       <c r="IV25" s="40"/>
     </row>
     <row r="26" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="106"/>
-      <c r="B26" s="56" t="s">
+      <c r="A26" s="72"/>
+      <c r="B26" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="57"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="7">
         <v>-7.6550000000000002</v>
       </c>
@@ -5598,7 +5604,7 @@
         <v>23.7</v>
       </c>
       <c r="F26" s="15"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="77"/>
       <c r="H26" s="16" t="s">
         <v>93</v>
       </c>
@@ -5617,7 +5623,7 @@
       <c r="N26" s="31">
         <v>13661</v>
       </c>
-      <c r="P26" s="124" t="s">
+      <c r="P26" s="62" t="s">
         <v>95</v>
       </c>
       <c r="Q26" s="37" t="s">
@@ -5868,11 +5874,11 @@
       <c r="IV26" s="40"/>
     </row>
     <row r="27" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="106"/>
-      <c r="B27" s="56" t="s">
+      <c r="A27" s="72"/>
+      <c r="B27" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="57"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="7">
         <v>0.56100000000000005</v>
       </c>
@@ -5880,7 +5886,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F27" s="15"/>
-      <c r="G27" s="77"/>
+      <c r="G27" s="78"/>
       <c r="H27" s="16" t="s">
         <v>96</v>
       </c>
@@ -5899,7 +5905,7 @@
       <c r="N27" s="31">
         <v>5261</v>
       </c>
-      <c r="P27" s="125"/>
+      <c r="P27" s="63"/>
       <c r="Q27" s="37" t="s">
         <v>88</v>
       </c>
@@ -6148,11 +6154,11 @@
       <c r="IV27" s="40"/>
     </row>
     <row r="28" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106"/>
-      <c r="B28" s="56" t="s">
+      <c r="A28" s="72"/>
+      <c r="B28" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="57"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="7">
         <v>-1.802</v>
       </c>
@@ -6160,12 +6166,12 @@
         <v>3.4</v>
       </c>
       <c r="F28" s="15"/>
-      <c r="G28" s="108" t="s">
+      <c r="G28" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="H28" s="114"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="6" t="s">
+      <c r="H28" s="93"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="52" t="s">
         <v>99</v>
       </c>
       <c r="L28" s="20" t="s">
@@ -6177,7 +6183,7 @@
       <c r="N28" s="7">
         <v>469678632</v>
       </c>
-      <c r="P28" s="125"/>
+      <c r="P28" s="63"/>
       <c r="Q28" s="37" t="s">
         <v>101</v>
       </c>
@@ -6426,11 +6432,11 @@
       <c r="IV28" s="40"/>
     </row>
     <row r="29" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
-      <c r="B29" s="56" t="s">
+      <c r="A29" s="73"/>
+      <c r="B29" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="57"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="7">
         <v>-1.4</v>
       </c>
@@ -6438,15 +6444,15 @@
         <v>-1.9</v>
       </c>
       <c r="F29" s="15"/>
-      <c r="G29" s="63" t="s">
+      <c r="G29" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="84"/>
       <c r="J29" s="7">
         <v>883</v>
       </c>
-      <c r="L29" s="117" t="s">
+      <c r="L29" s="50" t="s">
         <v>103</v>
       </c>
       <c r="M29" s="6" t="s">
@@ -6455,7 +6461,7 @@
       <c r="N29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="P29" s="126"/>
+      <c r="P29" s="64"/>
       <c r="Q29" s="37" t="s">
         <v>92</v>
       </c>
@@ -6704,11 +6710,11 @@
       <c r="IV29" s="40"/>
     </row>
     <row r="30" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="111" t="s">
+      <c r="A30" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="112"/>
-      <c r="C30" s="113"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="92"/>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
@@ -6716,11 +6722,11 @@
         <v>8</v>
       </c>
       <c r="F30" s="15"/>
-      <c r="G30" s="63" t="s">
+      <c r="G30" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="84"/>
       <c r="J30" s="7">
         <v>801</v>
       </c>
@@ -6733,7 +6739,7 @@
       <c r="N30" s="7">
         <v>15</v>
       </c>
-      <c r="P30" s="124" t="s">
+      <c r="P30" s="62" t="s">
         <v>108</v>
       </c>
       <c r="Q30" s="37" t="s">
@@ -6984,11 +6990,11 @@
       <c r="IV30" s="40"/>
     </row>
     <row r="31" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="81"/>
       <c r="D31" s="9" t="s">
         <v>111</v>
       </c>
@@ -6996,11 +7002,11 @@
         <v>6.32</v>
       </c>
       <c r="F31" s="15"/>
-      <c r="G31" s="63" t="s">
+      <c r="G31" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="64"/>
-      <c r="I31" s="65"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="84"/>
       <c r="J31" s="7">
         <v>747</v>
       </c>
@@ -7013,7 +7019,7 @@
       <c r="N31" s="7">
         <v>15</v>
       </c>
-      <c r="P31" s="126"/>
+      <c r="P31" s="64"/>
       <c r="Q31" s="37" t="s">
         <v>114</v>
       </c>
@@ -7262,11 +7268,11 @@
       <c r="IV31" s="40"/>
     </row>
     <row r="32" spans="1:256" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="9" t="s">
         <v>116</v>
       </c>
@@ -7274,11 +7280,11 @@
         <v>187.03</v>
       </c>
       <c r="F32" s="15"/>
-      <c r="G32" s="63" t="s">
+      <c r="G32" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="H32" s="64"/>
-      <c r="I32" s="65"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="84"/>
       <c r="J32" s="7">
         <v>708</v>
       </c>
@@ -7291,10 +7297,10 @@
       <c r="N32" s="7">
         <v>0</v>
       </c>
-      <c r="P32" s="108" t="s">
+      <c r="P32" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="Q32" s="123"/>
+      <c r="Q32" s="86"/>
       <c r="R32" s="6" t="s">
         <v>120</v>
       </c>
@@ -7303,11 +7309,11 @@
       </c>
     </row>
     <row r="33" spans="1:20" s="1" customFormat="1" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="81"/>
       <c r="D33" s="9" t="s">
         <v>123</v>
       </c>
@@ -7315,11 +7321,11 @@
         <v>1.92</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="63" t="s">
+      <c r="G33" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="H33" s="64"/>
-      <c r="I33" s="65"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="84"/>
       <c r="J33" s="7">
         <v>453</v>
       </c>
@@ -7334,10 +7340,10 @@
         <v>36</v>
       </c>
       <c r="O33" s="2"/>
-      <c r="P33" s="51" t="s">
+      <c r="P33" s="130" t="s">
         <v>126</v>
       </c>
-      <c r="Q33" s="69"/>
+      <c r="Q33" s="131"/>
       <c r="R33" s="7">
         <v>58</v>
       </c>
@@ -7352,11 +7358,11 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="15"/>
-      <c r="G34" s="70" t="s">
+      <c r="G34" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="71"/>
-      <c r="I34" s="72"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="67"/>
       <c r="J34" s="7">
         <v>7088</v>
       </c>
@@ -7371,7 +7377,7 @@
         <v>12</v>
       </c>
       <c r="O34" s="2"/>
-      <c r="P34" s="127" t="s">
+      <c r="P34" s="54" t="s">
         <v>129</v>
       </c>
       <c r="Q34" s="42" t="s">
@@ -7400,7 +7406,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="128"/>
+      <c r="P35" s="55"/>
       <c r="Q35" s="42" t="s">
         <v>131</v>
       </c>
@@ -7412,24 +7418,24 @@
       </c>
     </row>
     <row r="36" spans="1:20" s="1" customFormat="1" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="89" t="s">
+      <c r="A36" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
-      <c r="P36" s="128"/>
+      <c r="P36" s="55"/>
       <c r="Q36" s="42" t="s">
         <v>133</v>
       </c>
@@ -7441,22 +7447,22 @@
       </c>
     </row>
     <row r="37" spans="1:20" s="1" customFormat="1" ht="31.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="89"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="89"/>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="89"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
-      <c r="P37" s="129"/>
+      <c r="P37" s="56"/>
       <c r="Q37" s="42" t="s">
         <v>134</v>
       </c>
@@ -7468,78 +7474,78 @@
       </c>
     </row>
     <row r="38" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="P38" s="94" t="s">
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="P38" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="Q38" s="95"/>
-      <c r="R38" s="95"/>
-      <c r="S38" s="95"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="60"/>
     </row>
     <row r="39" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="89"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="89"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
       <c r="O39" s="32"/>
-      <c r="P39" s="96"/>
-      <c r="Q39" s="96"/>
-      <c r="R39" s="96"/>
-      <c r="S39" s="96"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="61"/>
       <c r="T39" s="15"/>
     </row>
     <row r="40" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="89"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
       <c r="O40" s="32"/>
-      <c r="P40" s="96"/>
-      <c r="Q40" s="96"/>
-      <c r="R40" s="96"/>
-      <c r="S40" s="96"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="61"/>
       <c r="T40" s="15"/>
     </row>
     <row r="41" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="90"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
       <c r="M41" s="33"/>
       <c r="N41" s="33"/>
       <c r="P41" s="34"/>
@@ -7548,22 +7554,22 @@
       <c r="S41" s="44"/>
     </row>
     <row r="42" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="91" t="s">
+      <c r="A42" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="B42" s="92"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="92"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
-      <c r="L42" s="92"/>
-      <c r="M42" s="92"/>
-      <c r="N42" s="93"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="69"/>
+      <c r="L42" s="69"/>
+      <c r="M42" s="69"/>
+      <c r="N42" s="70"/>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
       <c r="Q42" s="33"/>
@@ -7694,15 +7700,44 @@
     <protectedRange sqref="B25:C29" name="Budget titles_3"/>
   </protectedRanges>
   <mergeCells count="70">
-    <mergeCell ref="P34:P37"/>
-    <mergeCell ref="A36:L41"/>
-    <mergeCell ref="P38:S40"/>
-    <mergeCell ref="P15:P20"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="P23:P25"/>
-    <mergeCell ref="P26:P29"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="P6:S6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A42:N42"/>
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A19:A23"/>
@@ -7715,55 +7750,26 @@
     <mergeCell ref="G25:G27"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="G32:I32"/>
-    <mergeCell ref="P32:Q32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="G33:I33"/>
-    <mergeCell ref="P33:Q33"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="G29:I29"/>
+    <mergeCell ref="P34:P37"/>
+    <mergeCell ref="A36:L41"/>
+    <mergeCell ref="P38:S40"/>
+    <mergeCell ref="P15:P20"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="P23:P25"/>
+    <mergeCell ref="P26:P29"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="P6:S6"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="P3:S3"/>
   </mergeCells>
   <conditionalFormatting sqref="J7:J27 S7:S13 S15:S31 R33:S37 E31:E33">
     <cfRule type="cellIs" dxfId="13" priority="133" stopIfTrue="1" operator="equal">
@@ -7825,13 +7831,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<label version="1.0">
-  <element uid="id_unclassified"/>
-  <element uid="id_newpolicy" value=""/>
-</label>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
   <rangeList sheetStid="1" master="" otherUserPermission="visible">
     <arrUserId title="Results" rangeCreator="" othersAccessPermission="edit"/>
@@ -7851,17 +7850,24 @@
 </allowEditUser>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0699169F-FD5A-4B28-97D9-BF3F971E368D}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<label version="1.0">
+  <element uid="id_unclassified"/>
+  <element uid="id_newpolicy" value=""/>
+</label>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0699169F-FD5A-4B28-97D9-BF3F971E368D}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>